--- a/Result/profitability/4743.xlsx
+++ b/Result/profitability/4743.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
         <v>-0.02</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5487500000000001</v>
+        <v>-0.3512500000000001</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -772,7 +772,7 @@
         <v>0.58</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3437500000000001</v>
+        <v>-0.1762500000000001</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -879,7 +879,7 @@
         <v>0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2337500000000001</v>
+        <v>-0.1262500000000001</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -988,11 +988,11 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2000000000000001</v>
+        <v>0.08499999999999994</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1103,7 +1103,7 @@
         <v>0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03624999999999994</v>
+        <v>0.1024999999999999</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1222,11 +1222,11 @@
         <v>0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04749999999999994</v>
+        <v>0.1212499999999999</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>-0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03874999999999994</v>
+        <v>0.1424999999999999</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -1470,7 +1470,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06874999999999992</v>
+        <v>0.06874999999999994</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
@@ -9359,6 +9359,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4743</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>40</v>
+      </c>
+      <c r="D72" t="n">
+        <v>19</v>
+      </c>
+      <c r="E72" t="n">
+        <v>21</v>
+      </c>
+      <c r="F72" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-205</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-514.87%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>464</v>
+      </c>
+      <c r="J72" t="n">
+        <v>258</v>
+      </c>
+      <c r="K72" t="n">
+        <v>250</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-0.4812500000000001</v>
+      </c>
+      <c r="N72" t="n">
+        <v>35.67875</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-2.67741935483871</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>33.11</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>1.762107503991485</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-1.295454545454545</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>2.818984547461369</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
